--- a/F-Data-charts_pdf/summary_results.xlsx
+++ b/F-Data-charts_pdf/summary_results.xlsx
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24.2239</v>
+        <v>32.4274</v>
       </c>
     </row>
     <row r="39">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>181.3391</v>
+        <v>270.265</v>
       </c>
     </row>
     <row r="40">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="41">
